--- a/exports/xlsx/KPI_CHAMBRES_PATHOLOGIE.xlsx
+++ b/exports/xlsx/KPI_CHAMBRES_PATHOLOGIE.xlsx
@@ -459,7 +459,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -1083,7 +1083,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57">
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71">
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="92">
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="C110" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="111">
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="119">
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="133">
@@ -2162,7 +2162,7 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="134">
@@ -2240,7 +2240,7 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="140">
@@ -2396,7 +2396,7 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="152">
@@ -2526,7 +2526,7 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="162">
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="163">
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c r="C189" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="190">
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="221">
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="C280" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="281">
@@ -4632,7 +4632,7 @@
         </is>
       </c>
       <c r="C323" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="324">
@@ -5113,7 +5113,7 @@
         </is>
       </c>
       <c r="C360" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="361">
@@ -5321,7 +5321,7 @@
         </is>
       </c>
       <c r="C376" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="377">
@@ -5555,7 +5555,7 @@
         </is>
       </c>
       <c r="C394" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="395">
@@ -5633,7 +5633,7 @@
         </is>
       </c>
       <c r="C400" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="401">
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="C406" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="407">
@@ -5945,7 +5945,7 @@
         </is>
       </c>
       <c r="C424" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="425">
@@ -5984,7 +5984,7 @@
         </is>
       </c>
       <c r="C427" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="428">
@@ -6049,7 +6049,7 @@
         </is>
       </c>
       <c r="C432" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="433">
@@ -6140,7 +6140,7 @@
         </is>
       </c>
       <c r="C439" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="440">
@@ -6166,7 +6166,7 @@
         </is>
       </c>
       <c r="C441" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="442">
@@ -6231,7 +6231,7 @@
         </is>
       </c>
       <c r="C446" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="447">
@@ -6413,7 +6413,7 @@
         </is>
       </c>
       <c r="C460" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="461">
@@ -6452,7 +6452,7 @@
         </is>
       </c>
       <c r="C463" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="464">
@@ -6465,7 +6465,7 @@
         </is>
       </c>
       <c r="C464" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="465">
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="C466" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="467">
@@ -6504,7 +6504,7 @@
         </is>
       </c>
       <c r="C467" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="468">
@@ -6712,7 +6712,7 @@
         </is>
       </c>
       <c r="C483" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="484">
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="C484" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="485">
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="C488" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="489">
@@ -7206,7 +7206,7 @@
         </is>
       </c>
       <c r="C521" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="522">
@@ -7804,7 +7804,7 @@
         </is>
       </c>
       <c r="C567" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="568">
@@ -7921,7 +7921,7 @@
         </is>
       </c>
       <c r="C576" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="577">
@@ -7934,7 +7934,7 @@
         </is>
       </c>
       <c r="C577" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="578">
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="C580" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="581">
@@ -8103,7 +8103,7 @@
         </is>
       </c>
       <c r="C590" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="591">
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="C598" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="599">
@@ -8493,7 +8493,7 @@
         </is>
       </c>
       <c r="C620" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="621">
@@ -8571,7 +8571,7 @@
         </is>
       </c>
       <c r="C626" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="627">
@@ -8779,7 +8779,7 @@
         </is>
       </c>
       <c r="C642" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="643">
@@ -8818,7 +8818,7 @@
         </is>
       </c>
       <c r="C645" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="646">
@@ -8948,7 +8948,7 @@
         </is>
       </c>
       <c r="C655" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="656">
@@ -8961,7 +8961,7 @@
         </is>
       </c>
       <c r="C656" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="657">
@@ -9026,7 +9026,7 @@
         </is>
       </c>
       <c r="C661" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="662">
@@ -9065,7 +9065,7 @@
         </is>
       </c>
       <c r="C664" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="665">
@@ -9208,7 +9208,7 @@
         </is>
       </c>
       <c r="C675" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="676">
@@ -9234,7 +9234,7 @@
         </is>
       </c>
       <c r="C677" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="678">
@@ -9260,7 +9260,7 @@
         </is>
       </c>
       <c r="C679" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="680">
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="C680" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="681">
@@ -9286,7 +9286,7 @@
         </is>
       </c>
       <c r="C681" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="682">
@@ -9338,7 +9338,7 @@
         </is>
       </c>
       <c r="C685" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="686">
@@ -9364,7 +9364,7 @@
         </is>
       </c>
       <c r="C687" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="688">
@@ -9481,7 +9481,7 @@
         </is>
       </c>
       <c r="C696" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="697">
@@ -9702,7 +9702,7 @@
         </is>
       </c>
       <c r="C713" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="714">
@@ -9988,7 +9988,7 @@
         </is>
       </c>
       <c r="C735" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="736">
@@ -10001,7 +10001,7 @@
         </is>
       </c>
       <c r="C736" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="737">
@@ -10196,7 +10196,7 @@
         </is>
       </c>
       <c r="C751" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="752">
@@ -10300,7 +10300,7 @@
         </is>
       </c>
       <c r="C759" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="760">
@@ -10417,7 +10417,7 @@
         </is>
       </c>
       <c r="C768" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="769">
@@ -10430,7 +10430,7 @@
         </is>
       </c>
       <c r="C769" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="770">
@@ -10599,7 +10599,7 @@
         </is>
       </c>
       <c r="C782" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="783">
@@ -10612,7 +10612,7 @@
         </is>
       </c>
       <c r="C783" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="784">
@@ -10677,7 +10677,7 @@
         </is>
       </c>
       <c r="C788" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="789">
@@ -10885,7 +10885,7 @@
         </is>
       </c>
       <c r="C804" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="805">
@@ -10950,7 +10950,7 @@
         </is>
       </c>
       <c r="C809" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="810">
@@ -11275,7 +11275,7 @@
         </is>
       </c>
       <c r="C834" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="835">
@@ -11288,7 +11288,7 @@
         </is>
       </c>
       <c r="C835" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="836">
@@ -11470,7 +11470,7 @@
         </is>
       </c>
       <c r="C849" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="850">
@@ -11756,7 +11756,7 @@
         </is>
       </c>
       <c r="C871" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="872">
@@ -11782,7 +11782,7 @@
         </is>
       </c>
       <c r="C873" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="874">
@@ -11808,7 +11808,7 @@
         </is>
       </c>
       <c r="C875" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="876">
@@ -11899,7 +11899,7 @@
         </is>
       </c>
       <c r="C882" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="883">
@@ -11925,7 +11925,7 @@
         </is>
       </c>
       <c r="C884" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="885">
@@ -12016,7 +12016,7 @@
         </is>
       </c>
       <c r="C891" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="892">
@@ -12107,7 +12107,7 @@
         </is>
       </c>
       <c r="C898" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="899">
@@ -12289,7 +12289,7 @@
         </is>
       </c>
       <c r="C912" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="913">
@@ -12315,7 +12315,7 @@
         </is>
       </c>
       <c r="C914" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="915">
@@ -12406,7 +12406,7 @@
         </is>
       </c>
       <c r="C921" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="922">
@@ -12549,7 +12549,7 @@
         </is>
       </c>
       <c r="C932" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="933">
@@ -12653,7 +12653,7 @@
         </is>
       </c>
       <c r="C940" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="941">
@@ -12718,7 +12718,7 @@
         </is>
       </c>
       <c r="C945" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="946">
@@ -12731,7 +12731,7 @@
         </is>
       </c>
       <c r="C946" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="947">
@@ -12822,7 +12822,7 @@
         </is>
       </c>
       <c r="C953" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="954">
@@ -12900,7 +12900,7 @@
         </is>
       </c>
       <c r="C959" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="960">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="C963" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="964">
@@ -13004,7 +13004,7 @@
         </is>
       </c>
       <c r="C967" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="968">
@@ -13017,7 +13017,7 @@
         </is>
       </c>
       <c r="C968" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="969">
@@ -13030,7 +13030,7 @@
         </is>
       </c>
       <c r="C969" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="970">
@@ -13056,7 +13056,7 @@
         </is>
       </c>
       <c r="C971" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="972">
@@ -13069,7 +13069,7 @@
         </is>
       </c>
       <c r="C972" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="973">
@@ -13238,7 +13238,7 @@
         </is>
       </c>
       <c r="C985" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="986">
@@ -13251,7 +13251,7 @@
         </is>
       </c>
       <c r="C986" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="987">
@@ -13680,7 +13680,7 @@
         </is>
       </c>
       <c r="C1019" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1020">
@@ -13693,7 +13693,7 @@
         </is>
       </c>
       <c r="C1020" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1021">
@@ -13732,7 +13732,7 @@
         </is>
       </c>
       <c r="C1023" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1024">
@@ -14187,7 +14187,7 @@
         </is>
       </c>
       <c r="C1058" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1059">
@@ -14356,7 +14356,7 @@
         </is>
       </c>
       <c r="C1071" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1072">
@@ -14733,7 +14733,7 @@
         </is>
       </c>
       <c r="C1100" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1101">
@@ -14746,7 +14746,7 @@
         </is>
       </c>
       <c r="C1101" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1102">
@@ -14798,7 +14798,7 @@
         </is>
       </c>
       <c r="C1105" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1106">
@@ -14889,7 +14889,7 @@
         </is>
       </c>
       <c r="C1112" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1113">
@@ -14928,7 +14928,7 @@
         </is>
       </c>
       <c r="C1115" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1116">
@@ -14954,7 +14954,7 @@
         </is>
       </c>
       <c r="C1117" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1118">
@@ -15032,7 +15032,7 @@
         </is>
       </c>
       <c r="C1123" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1124">
@@ -15045,7 +15045,7 @@
         </is>
       </c>
       <c r="C1124" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1125">
@@ -15149,7 +15149,7 @@
         </is>
       </c>
       <c r="C1132" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1133">
@@ -15162,7 +15162,7 @@
         </is>
       </c>
       <c r="C1133" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1134">
@@ -15370,7 +15370,7 @@
         </is>
       </c>
       <c r="C1149" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1150">
@@ -15383,7 +15383,7 @@
         </is>
       </c>
       <c r="C1150" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1151">
@@ -15409,7 +15409,7 @@
         </is>
       </c>
       <c r="C1152" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1153">
@@ -15422,7 +15422,7 @@
         </is>
       </c>
       <c r="C1153" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1154">
@@ -15539,7 +15539,7 @@
         </is>
       </c>
       <c r="C1162" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1163">
@@ -15695,7 +15695,7 @@
         </is>
       </c>
       <c r="C1174" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1175">
@@ -15721,7 +15721,7 @@
         </is>
       </c>
       <c r="C1176" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1177">
@@ -15773,7 +15773,7 @@
         </is>
       </c>
       <c r="C1180" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1181">
@@ -15812,7 +15812,7 @@
         </is>
       </c>
       <c r="C1183" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1184">
@@ -15825,7 +15825,7 @@
         </is>
       </c>
       <c r="C1184" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1185">
